--- a/templates/planeamento_template.xlsx
+++ b/templates/planeamento_template.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="EsteLivro" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807AC95C-7FFF-46A3-863D-73D7C8006A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D8A3F8-56FA-4307-ADDF-C5152281C64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,13 +82,13 @@
     <t>SERVIÇO GERAL</t>
   </si>
   <si>
-    <t>Processado Por: SALOC 360</t>
-  </si>
-  <si>
     <t>PLANEAMENTO DIÁRIO</t>
   </si>
   <si>
     <t>Observações</t>
+  </si>
+  <si>
+    <t>Processado Por: CB360 Online</t>
   </si>
 </sst>
 </file>
@@ -342,32 +342,32 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,9 +491,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -531,7 +531,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -637,7 +637,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -779,7 +779,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -803,14 +803,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -823,103 +823,103 @@
     <row r="9" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
+      <c r="B11" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="29"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="31"/>
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30" t="s">
+      <c r="F17" s="32"/>
+      <c r="G17" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="30" t="s">
+      <c r="H17" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I17" s="30" t="s">
-        <v>20</v>
+      <c r="I17" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="J17" s="5"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="31"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
       <c r="E18" s="20" t="s">
         <v>7</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
       <c r="J18" s="5"/>
     </row>
     <row r="19" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -935,56 +935,56 @@
     </row>
     <row r="20" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="29"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="31"/>
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30" t="s">
+      <c r="F22" s="32"/>
+      <c r="G22" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="30" t="s">
+      <c r="H22" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I22" s="30" t="s">
-        <v>20</v>
+      <c r="I22" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="J22" s="5"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="31"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
       <c r="E23" s="20" t="s">
         <v>7</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
       <c r="J23" s="5"/>
     </row>
     <row r="24" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1000,56 +1000,56 @@
     </row>
     <row r="25" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="29"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="31"/>
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30" t="s">
+      <c r="F27" s="32"/>
+      <c r="G27" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H27" s="30" t="s">
+      <c r="H27" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I27" s="30" t="s">
-        <v>20</v>
+      <c r="I27" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="31"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
       <c r="E28" s="20" t="s">
         <v>7</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
       <c r="J28" s="5"/>
     </row>
     <row r="29" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1065,56 +1065,56 @@
     </row>
     <row r="30" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="29"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="31"/>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="30" t="s">
+      <c r="E32" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30" t="s">
+      <c r="F32" s="32"/>
+      <c r="G32" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H32" s="30" t="s">
+      <c r="H32" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I32" s="30" t="s">
-        <v>20</v>
+      <c r="I32" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="J32" s="5"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="31"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
       <c r="E33" s="20" t="s">
         <v>7</v>
       </c>
       <c r="F33" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
       <c r="J33" s="5"/>
     </row>
     <row r="34" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1184,56 +1184,56 @@
       <c r="J39" s="12"/>
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="29"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="31"/>
       <c r="J40" s="4"/>
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="31" t="s">
+      <c r="B41" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="30" t="s">
+      <c r="D41" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E41" s="30" t="s">
+      <c r="E41" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30" t="s">
+      <c r="F41" s="32"/>
+      <c r="G41" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H41" s="30" t="s">
+      <c r="H41" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I41" s="30" t="s">
-        <v>20</v>
+      <c r="I41" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="J41" s="5"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="31"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
       <c r="E42" s="20" t="s">
         <v>7</v>
       </c>
       <c r="F42" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
       <c r="J42" s="5"/>
     </row>
     <row r="43" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1293,56 +1293,56 @@
     </row>
     <row r="48" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="29"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="31"/>
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="31" t="s">
+      <c r="B50" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C50" s="30" t="s">
+      <c r="C50" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D50" s="30" t="s">
+      <c r="D50" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E50" s="30" t="s">
+      <c r="E50" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30" t="s">
+      <c r="F50" s="32"/>
+      <c r="G50" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H50" s="30" t="s">
+      <c r="H50" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I50" s="30" t="s">
-        <v>20</v>
+      <c r="I50" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="J50" s="5"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="31"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
       <c r="E51" s="20" t="s">
         <v>7</v>
       </c>
       <c r="F51" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1401,56 +1401,56 @@
     </row>
     <row r="54" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="29"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="31"/>
       <c r="J55" s="4"/>
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="31" t="s">
+      <c r="B56" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C56" s="30" t="s">
+      <c r="C56" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D56" s="30" t="s">
+      <c r="D56" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E56" s="30" t="s">
+      <c r="E56" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30" t="s">
+      <c r="F56" s="32"/>
+      <c r="G56" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H56" s="30" t="s">
+      <c r="H56" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I56" s="30" t="s">
-        <v>20</v>
+      <c r="I56" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="J56" s="5"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="31"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
       <c r="E57" s="20" t="s">
         <v>7</v>
       </c>
       <c r="F57" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
       <c r="J57" s="5"/>
     </row>
     <row r="58" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1536,56 +1536,56 @@
     </row>
     <row r="61" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="27" t="s">
+      <c r="B62" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C62" s="28"/>
-      <c r="D62" s="28"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="29"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="31"/>
       <c r="J62" s="4"/>
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="31" t="s">
+      <c r="B63" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C63" s="30" t="s">
+      <c r="C63" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D63" s="30" t="s">
+      <c r="D63" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E63" s="30" t="s">
+      <c r="E63" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F63" s="30"/>
-      <c r="G63" s="30" t="s">
+      <c r="F63" s="32"/>
+      <c r="G63" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H63" s="30" t="s">
+      <c r="H63" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I63" s="30" t="s">
-        <v>20</v>
+      <c r="I63" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="J63" s="5"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="31"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
       <c r="E64" s="20" t="s">
         <v>7</v>
       </c>
       <c r="F64" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
       <c r="J64" s="5"/>
     </row>
     <row r="65" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1671,56 +1671,56 @@
     </row>
     <row r="68" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="27" t="s">
+      <c r="B69" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="29"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="31"/>
       <c r="J69" s="4"/>
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="31" t="s">
+      <c r="B70" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="30" t="s">
+      <c r="C70" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="30" t="s">
+      <c r="D70" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E70" s="30" t="s">
+      <c r="E70" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30" t="s">
+      <c r="F70" s="32"/>
+      <c r="G70" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="30" t="s">
+      <c r="H70" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I70" s="30" t="s">
-        <v>20</v>
+      <c r="I70" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="J70" s="5"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B71" s="31"/>
-      <c r="C71" s="30"/>
-      <c r="D71" s="30"/>
+      <c r="B71" s="33"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
       <c r="E71" s="20" t="s">
         <v>7</v>
       </c>
       <c r="F71" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="30"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
       <c r="J71" s="5"/>
     </row>
     <row r="72" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2005,21 +2005,83 @@
       <c r="J82" s="14"/>
     </row>
     <row r="83" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="26" t="str">
-        <f ca="1">"Última atualização às: "&amp;TEXT(NOW(),"hh:mm")</f>
-        <v>Última atualização às: 10:29</v>
-      </c>
-      <c r="C83" s="26"/>
+      <c r="B83" s="34"/>
+      <c r="C83" s="34"/>
       <c r="D83" s="17"/>
       <c r="E83" s="18"/>
       <c r="I83" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.25"/>
     <row r="85" spans="2:10" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B11:I13"/>
     <mergeCell ref="B14:I14"/>
@@ -2031,71 +2093,6 @@
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="I17:I18"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B69:I69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="I70:I71"/>
   </mergeCells>
   <conditionalFormatting sqref="G19:H19 G24:H24 G29:H29 G34:H38 G43:H47 G52:H53 G58:H60 G65:H67 G72:H81">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
